--- a/statistics/statistics.xlsx
+++ b/statistics/statistics.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sciebo\TISMIR NTCB\figures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\axelb\Sciebo\TISMIR NTCB\figures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF02D51D-CC89-4F97-8E57-E38569F44ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B120A01-C0E7-448E-B6A9-0752141648CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{553881A2-DFB8-4FB4-8655-005BE24C585B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{553881A2-DFB8-4FB4-8655-005BE24C585B}"/>
   </bookViews>
   <sheets>
     <sheet name="Meter Signatures" sheetId="5" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="205">
   <si>
     <t>Interval</t>
   </si>
@@ -715,6 +715,9 @@
     <t>P1
 P5</t>
   </si>
+  <si>
+    <t>%</t>
+  </si>
 </sst>
 </file>
 
@@ -933,7 +936,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>bass</c:v>
+            <c:v>soprano</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1236,7 +1239,7 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>tenor</c:v>
+            <c:v>alto</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1539,7 +1542,7 @@
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
-            <c:v>alto</c:v>
+            <c:v>tenor</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1842,7 +1845,7 @@
           <c:idx val="3"/>
           <c:order val="3"/>
           <c:tx>
-            <c:v>soprano</c:v>
+            <c:v>bass</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -25246,227 +25249,309 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2782000A-4CB0-4A0C-AF1F-EDB205E99486}">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" style="4" customWidth="1"/>
     <col min="2" max="2" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>93</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>111</v>
       </c>
       <c r="B2">
         <v>1302</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2" cm="1">
+        <f t="array" ref="C2:C27">100*B2:B27/SUM(B2:B27)</f>
+        <v>36.758893280632414</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>108</v>
       </c>
       <c r="B3">
         <v>459</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3">
+        <v>12.958780350084698</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>94</v>
       </c>
       <c r="B4">
         <v>454</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C4">
+        <v>12.817617165443252</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>112</v>
       </c>
       <c r="B5">
         <v>340</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C5">
+        <v>9.5990965556182939</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>113</v>
       </c>
       <c r="B6">
         <v>273</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C6">
+        <v>7.7075098814229248</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>110</v>
       </c>
       <c r="B7">
         <v>250</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C7">
+        <v>7.0581592320722759</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>95</v>
       </c>
       <c r="B8">
         <v>159</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C8">
+        <v>4.4889892715979673</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>96</v>
       </c>
       <c r="B9">
         <v>73</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C9">
+        <v>2.0609824957651046</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>97</v>
       </c>
       <c r="B10">
         <v>72</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10">
+        <v>2.0327498588368154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>114</v>
       </c>
       <c r="B11">
         <v>36</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C11">
+        <v>1.0163749294184077</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>106</v>
       </c>
       <c r="B12">
         <v>30</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C12">
+        <v>0.84697910784867303</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>99</v>
       </c>
       <c r="B13">
         <v>25</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C13">
+        <v>0.70581592320722752</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>107</v>
       </c>
       <c r="B14">
         <v>16</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C14">
+        <v>0.45172219085262566</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>104</v>
       </c>
       <c r="B15">
         <v>13</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C15">
+        <v>0.36702428006775834</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>119</v>
       </c>
       <c r="B16">
         <v>11</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C16">
+        <v>0.3105590062111801</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B17">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C17">
+        <v>0.28232636928289101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B18">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C18">
+        <v>0.1411631846414455</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>105</v>
       </c>
       <c r="B19">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C19">
+        <v>0.11293054771315642</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>98</v>
       </c>
       <c r="B20">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C20">
+        <v>8.4697910784867311E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>100</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C21">
+        <v>2.8232636928289104E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B22" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C22">
+        <v>2.8232636928289104E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>102</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C23">
+        <v>2.8232636928289104E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>103</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C24">
+        <v>2.8232636928289104E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>109</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C25">
+        <v>2.8232636928289104E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>116</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C26">
+        <v>2.8232636928289104E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B27">
         <v>1</v>
+      </c>
+      <c r="C27">
+        <v>2.8232636928289104E-2</v>
       </c>
     </row>
   </sheetData>
